--- a/兆妤/112~114年花蓮縣公路客運持卡身分分析/112~114年花蓮縣公路客運持卡身分統計表.xlsx
+++ b/兆妤/112~114年花蓮縣公路客運持卡身分分析/112~114年花蓮縣公路客運持卡身分統計表.xlsx
@@ -1,71 +1,145 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\115_Midterm-Report\兆妤\112~114年花蓮縣公路客運持卡身分分析\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6D2AC5-F8B0-4185-AB9D-D68712BE87DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="人數表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="比例表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="人數表" sheetId="1" r:id="rId1"/>
+    <sheet name="比例表" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">普通(含TPASS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">學生</t>
-  </si>
-  <si>
-    <t xml:space="preserve">敬老優待</t>
-  </si>
-  <si>
-    <t xml:space="preserve">愛心優待</t>
-  </si>
-  <si>
-    <t xml:space="preserve">其他優待</t>
-  </si>
-  <si>
-    <t xml:space="preserve">員工</t>
-  </si>
-  <si>
-    <t xml:space="preserve">無法區別</t>
-  </si>
-  <si>
-    <t xml:space="preserve">總運量</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>普通(含TPASS)</t>
+  </si>
+  <si>
+    <t>學生</t>
+  </si>
+  <si>
+    <t>敬老優待</t>
+  </si>
+  <si>
+    <t>愛心優待</t>
+  </si>
+  <si>
+    <t>其他優待</t>
+  </si>
+  <si>
+    <t>員工</t>
+  </si>
+  <si>
+    <t>無法區別</t>
+  </si>
+  <si>
+    <t>總運量</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <r>
+      <t>113</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>年成長率</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>114</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>年成長率</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="176" formatCode="0.0%"/>
+    <numFmt numFmtId="177" formatCode="#,##0_ "/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -85,16 +159,37 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -376,11 +471,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -393,131 +492,304 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2">
         <v>167971</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2">
         <v>200482</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2">
         <v>153128</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
+      <c r="E2" s="3">
+        <f>(C2-B2)/B2</f>
+        <v>0.19355126777836651</v>
+      </c>
+      <c r="F2" s="3">
+        <f>(D2-C2)/C2</f>
+        <v>-0.23620075617761196</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="4"/>
+      <c r="B3" s="1">
+        <v>0.41501578814727702</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.44468153064031002</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.425288218254332</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2">
+        <v>74152</v>
+      </c>
+      <c r="C4" s="2">
+        <v>125897</v>
+      </c>
+      <c r="D4" s="2">
+        <v>118456</v>
+      </c>
+      <c r="E4" s="3">
+        <f>(C4-B4)/B4</f>
+        <v>0.69782338979393677</v>
+      </c>
+      <c r="F4" s="3">
+        <f>(D4-C4)/C4</f>
+        <v>-5.9103870624399313E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="4"/>
+      <c r="B5" s="1">
+        <v>0.183211689652957</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.279247367160259</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.32899235398839599</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B6" s="2">
         <v>44587</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C6" s="2">
         <v>33262</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D6" s="2">
         <v>23325</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="n">
-        <v>74152</v>
-      </c>
-      <c r="C4" t="n">
-        <v>125897</v>
-      </c>
-      <c r="D4" t="n">
-        <v>118456</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
+      <c r="E6" s="3">
+        <f>(C6-B6)/B6</f>
+        <v>-0.25399780204992489</v>
+      </c>
+      <c r="F6" s="3">
+        <f>(D6-C6)/C6</f>
+        <v>-0.29874932355240214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="4"/>
+      <c r="B7" s="1">
+        <v>0.110163712463</v>
+      </c>
+      <c r="C7" s="1">
+        <v>7.37771823513233E-2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6.4781409610145099E-2</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B8" s="2">
         <v>23057</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C8" s="2">
         <v>40231</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D8" s="2">
         <v>46445</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
+      <c r="E8" s="3">
+        <f t="shared" ref="E4:F14" si="0">(C8-B8)/B8</f>
+        <v>0.74484972025848983</v>
+      </c>
+      <c r="F8" s="3">
+        <f t="shared" si="0"/>
+        <v>0.15445800502100371</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="4"/>
+      <c r="B9" s="1">
+        <v>5.6968280401448801E-2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>8.9234857289882993E-2</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.128993464923609</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B10" s="2">
         <v>93245</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C10" s="2">
         <v>42013</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D10" s="2">
         <v>6928</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
+      <c r="E10" s="3">
+        <f t="shared" si="0"/>
+        <v>-0.54943428602069821</v>
+      </c>
+      <c r="F10" s="3">
+        <f t="shared" si="0"/>
+        <v>-0.83509865993859045</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="4"/>
+      <c r="B11" s="1">
+        <v>0.23038588307382099</v>
+      </c>
+      <c r="C11" s="1">
+        <v>9.3187443993931404E-2</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1.9241397889778598E-2</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B12" s="2">
         <v>1722</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C12" s="2">
         <v>8959</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D12" s="2">
         <v>11775</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
+      <c r="E12" s="3">
+        <f t="shared" si="0"/>
+        <v>4.2026713124274098</v>
+      </c>
+      <c r="F12" s="3">
+        <f t="shared" si="0"/>
+        <v>0.31432079473155489</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="4"/>
+      <c r="B13" s="1">
+        <v>4.2546462614951996E-3</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1.98716185642927E-2</v>
+      </c>
+      <c r="D13" s="1">
+        <v>3.2703155333738798E-2</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B14" s="2">
         <v>404734</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C14" s="2">
         <v>450844</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D14" s="2">
         <v>360057</v>
       </c>
+      <c r="E14" s="3">
+        <f t="shared" si="0"/>
+        <v>0.11392667776860851</v>
+      </c>
+      <c r="F14" s="3">
+        <f t="shared" si="0"/>
+        <v>-0.20137120600473779</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="4"/>
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F12:F13"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,120 +803,121 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="n">
-        <v>0.415015788147277</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.44468153064031</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="B2" s="1">
+        <v>0.41501578814727702</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.44468153064031002</v>
+      </c>
+      <c r="D2" s="1">
         <v>0.425288218254332</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="1">
         <v>0.110163712463</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.0737771823513233</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.0647814096101451</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="C3" s="1">
+        <v>7.37771823513233E-2</v>
+      </c>
+      <c r="D3" s="1">
+        <v>6.4781409610145099E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="1">
         <v>0.183211689652957</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="1">
         <v>0.279247367160259</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.328992353988396</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="D4" s="1">
+        <v>0.32899235398839599</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="n">
-        <v>0.0569682804014488</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.089234857289883</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="B5" s="1">
+        <v>5.6968280401448801E-2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>8.9234857289882993E-2</v>
+      </c>
+      <c r="D5" s="1">
         <v>0.128993464923609</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="n">
-        <v>0.230385883073821</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.0931874439939314</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.0192413978897786</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="B6" s="1">
+        <v>0.23038588307382099</v>
+      </c>
+      <c r="C6" s="1">
+        <v>9.3187443993931404E-2</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1.9241397889778598E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="1">
         <v>0</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="1">
         <v>0</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.0042546462614952</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.0198716185642927</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.0327031553337388</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="B8" s="1">
+        <v>4.2546462614951996E-3</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1.98716185642927E-2</v>
+      </c>
+      <c r="D8" s="1">
+        <v>3.2703155333738798E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="1">
         <v>1</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="1">
         <v>1</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>